--- a/padel_2026.xlsx
+++ b/padel_2026.xlsx
@@ -3,22 +3,22 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="0" activeTab="5"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="resultados" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="listas" sheetId="19" state="visible" r:id="rId2"/>
     <sheet name="participantes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="clasificacion_auto" sheetId="175" state="visible" r:id="rId4"/>
-    <sheet name="clasificacion" sheetId="176" state="visible" r:id="rId5"/>
-    <sheet name="historial_partidos" sheetId="177" state="visible" r:id="rId6"/>
+    <sheet name="clasificacion_auto" sheetId="178" state="visible" r:id="rId4"/>
+    <sheet name="clasificacion" sheetId="179" state="visible" r:id="rId5"/>
+    <sheet name="historial_partidos" sheetId="180" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
   <si>
     <t>Mediocre alto</t>
   </si>
@@ -398,6 +398,24 @@
     <t>PUNTOS_ACUM</t>
   </si>
   <si>
+    <t>mediocre alto</t>
+  </si>
+  <si>
+    <t>1ª vuelta</t>
+  </si>
+  <si>
+    <t>Fla-Delicattesen</t>
+  </si>
+  <si>
+    <t>Gana</t>
+  </si>
+  <si>
+    <t>Ceci-Ángel</t>
+  </si>
+  <si>
+    <t>Pierde</t>
+  </si>
+  <si>
     <t xml:space="preserve">GRUPO</t>
   </si>
   <si>
@@ -434,6 +452,72 @@
     <t xml:space="preserve">JP</t>
   </si>
   <si>
+    <t xml:space="preserve">mediocre alto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fla-Delicattesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temes-Sergio Payo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrés-J.J.Varas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceci-Ángel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuño-Jorge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salva-Alberto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mediocre bajo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carmen-Mónica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cristina-Alberto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luis-Lina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mario-Lourdes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mediocre medio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teresa-Álvaro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alba-Bonilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alberto-Esperanza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leticia-Alfonso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miguel Ángel-Juanjo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tito-Yolanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tania-Laura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natalia-Jose Antonio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marta-Víctor</t>
+  </si>
+  <si>
     <t xml:space="preserve">P. JUGADOS</t>
   </si>
   <si>
@@ -452,6 +536,15 @@
     <t xml:space="preserve">SET PERDIDOS</t>
   </si>
   <si>
+    <t xml:space="preserve">Mediocre alto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mediocre medio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mediocre bajo</t>
+  </si>
+  <si>
     <t xml:space="preserve">FECHA</t>
   </si>
   <si>
@@ -467,19 +560,10 @@
     <t xml:space="preserve">PUNTOS_ACUM</t>
   </si>
   <si>
-    <t xml:space="preserve">mediocre alto</t>
-  </si>
-  <si>
     <t xml:space="preserve">1ª vuelta</t>
   </si>
   <si>
-    <t xml:space="preserve">Fla-Delicattesen</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceci-Ángel</t>
   </si>
   <si>
     <t xml:space="preserve">Pierde</t>
@@ -1630,40 +1714,762 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D1" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="H1" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="I1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="J1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="K1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="L1" t="s">
-        <v>137</v>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>151</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>153</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>151</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>154</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>151</v>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>157</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>158</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>159</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>156</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="s">
+        <v>160</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>161</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>156</v>
+      </c>
+      <c r="B17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>162</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>156</v>
+      </c>
+      <c r="B18" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>163</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>156</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>164</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>156</v>
+      </c>
+      <c r="B20" t="n">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>165</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1679,34 +2485,642 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D1" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E1" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="F1" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="G1" t="s">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="H1" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="I1" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="J1" t="s">
-        <v>143</v>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>173</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>173</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>159</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>161</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>173</v>
+      </c>
+      <c r="B13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>162</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>173</v>
+      </c>
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>163</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>173</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>164</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>173</v>
+      </c>
+      <c r="B16" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>165</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>174</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>152</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>174</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>154</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>174</v>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>155</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1722,43 +3136,43 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="B1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C1" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="D1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E1" t="s">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="F1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="G1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1" t="s">
         <v>135</v>
       </c>
-      <c r="H1" t="s">
-        <v>129</v>
-      </c>
       <c r="I1" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="J1" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="K1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="L1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="M1" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2">
@@ -1766,16 +3180,16 @@
         <v>46298</v>
       </c>
       <c r="B2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C2" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E2" t="s">
-        <v>152</v>
+        <v>181</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
@@ -1807,16 +3221,16 @@
         <v>46298</v>
       </c>
       <c r="B3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C3" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E3" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>

--- a/padel_2026.xlsx
+++ b/padel_2026.xlsx
@@ -3,22 +3,22 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="0" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="resultados" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="listas" sheetId="19" state="visible" r:id="rId2"/>
     <sheet name="participantes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="clasificacion_auto" sheetId="178" state="visible" r:id="rId4"/>
-    <sheet name="clasificacion" sheetId="179" state="visible" r:id="rId5"/>
-    <sheet name="historial_partidos" sheetId="180" state="visible" r:id="rId6"/>
+    <sheet name="clasificacion_auto" sheetId="181" state="visible" r:id="rId4"/>
+    <sheet name="clasificacion" sheetId="182" state="visible" r:id="rId5"/>
+    <sheet name="historial_partidos" sheetId="183" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="202">
   <si>
     <t>Mediocre alto</t>
   </si>
@@ -32,9 +32,6 @@
     <t>Nuño-Jorge</t>
   </si>
   <si>
-    <t>6-4, 6-2</t>
-  </si>
-  <si>
     <t>Tania-Laura</t>
   </si>
   <si>
@@ -65,9 +62,6 @@
     <t>RESULTADO_P2P1</t>
   </si>
   <si>
-    <t>4-6, 2-6</t>
-  </si>
-  <si>
     <t>NOMBRE</t>
   </si>
   <si>
@@ -365,6 +359,72 @@
     <t>JP</t>
   </si>
   <si>
+    <t>mediocre alto</t>
+  </si>
+  <si>
+    <t>Fla-Delicattesen</t>
+  </si>
+  <si>
+    <t>Temes-Sergio Payo</t>
+  </si>
+  <si>
+    <t>Andrés-J.J.Varas</t>
+  </si>
+  <si>
+    <t>Ceci-Ángel</t>
+  </si>
+  <si>
+    <t>Nuño-Jorge</t>
+  </si>
+  <si>
+    <t>Salva-Alberto</t>
+  </si>
+  <si>
+    <t>mediocre bajo</t>
+  </si>
+  <si>
+    <t>Carmen-Mónica</t>
+  </si>
+  <si>
+    <t>Cristina-Alberto</t>
+  </si>
+  <si>
+    <t>Luis-Lina</t>
+  </si>
+  <si>
+    <t>Mario-Lourdes</t>
+  </si>
+  <si>
+    <t>mediocre medio</t>
+  </si>
+  <si>
+    <t>Teresa-Álvaro</t>
+  </si>
+  <si>
+    <t>Alba-Bonilla</t>
+  </si>
+  <si>
+    <t>Alberto-Esperanza</t>
+  </si>
+  <si>
+    <t>Leticia-Alfonso</t>
+  </si>
+  <si>
+    <t>Miguel Ángel-Juanjo</t>
+  </si>
+  <si>
+    <t>Tito-Yolanda</t>
+  </si>
+  <si>
+    <t>Tania-Laura</t>
+  </si>
+  <si>
+    <t>Natalia-Jose Antonio</t>
+  </si>
+  <si>
+    <t>Marta-Víctor</t>
+  </si>
+  <si>
     <t>P. JUGADOS</t>
   </si>
   <si>
@@ -383,6 +443,15 @@
     <t>SET PERDIDOS</t>
   </si>
   <si>
+    <t>Mediocre alto</t>
+  </si>
+  <si>
+    <t>Mediocre medio</t>
+  </si>
+  <si>
+    <t>Mediocre bajo</t>
+  </si>
+  <si>
     <t>FECHA</t>
   </si>
   <si>
@@ -398,22 +467,10 @@
     <t>PUNTOS_ACUM</t>
   </si>
   <si>
-    <t>mediocre alto</t>
-  </si>
-  <si>
-    <t>1ª vuelta</t>
-  </si>
-  <si>
-    <t>Fla-Delicattesen</t>
-  </si>
-  <si>
-    <t>Gana</t>
-  </si>
-  <si>
-    <t>Ceci-Ángel</t>
-  </si>
-  <si>
-    <t>Pierde</t>
+    <t>6-4, 6-1</t>
+  </si>
+  <si>
+    <t>4-6, 1-6</t>
   </si>
   <si>
     <t xml:space="preserve">GRUPO</t>
@@ -491,19 +548,19 @@
     <t xml:space="preserve">mediocre medio</t>
   </si>
   <si>
+    <t xml:space="preserve">Leticia-Alfonso</t>
+  </si>
+  <si>
     <t xml:space="preserve">Teresa-Álvaro</t>
   </si>
   <si>
     <t xml:space="preserve">Alba-Bonilla</t>
   </si>
   <si>
+    <t xml:space="preserve">Miguel Ángel-Juanjo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alberto-Esperanza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leticia-Alfonso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miguel Ángel-Juanjo</t>
   </si>
   <si>
     <t xml:space="preserve">Tito-Yolanda</t>
@@ -950,52 +1007,52 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="16.5546875" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="16.54296875" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="13.6328125" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="19" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="17.109375" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="16.5546875" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="17.08984375" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="16.54296875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="E1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>4</v>
+        <v>149</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4">
@@ -1041,13 +1098,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
-        <v>9</v>
-      </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2">
@@ -1055,10 +1112,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -1066,10 +1123,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -1082,82 +1139,82 @@
     </row>
     <row r="5">
       <c r="C5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="C6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="C7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
       <c r="C8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
       <c r="C9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="C10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
       <c r="C12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="C13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="C14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="C15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="C16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
       <c r="C17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
       <c r="C18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="C19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20">
       <c r="C20" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1171,24 +1228,24 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="25.33203125" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="45.44140625" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="15.36328125" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="11.6328125" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="25.36328125" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="45.453125" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2">
@@ -1199,10 +1256,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -1213,10 +1270,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -1227,10 +1284,10 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
@@ -1241,10 +1298,10 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
@@ -1255,10 +1312,10 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7">
@@ -1269,10 +1326,10 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
@@ -1283,10 +1340,10 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9">
@@ -1297,7 +1354,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
@@ -1308,10 +1365,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
@@ -1322,10 +1379,10 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -1336,7 +1393,7 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13">
@@ -1347,7 +1404,7 @@
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14">
@@ -1358,10 +1415,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15">
@@ -1372,10 +1429,10 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -1386,10 +1443,10 @@
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -1400,10 +1457,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -1414,10 +1471,10 @@
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19">
@@ -1428,10 +1485,10 @@
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20">
@@ -1442,10 +1499,10 @@
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21">
@@ -1456,10 +1513,10 @@
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22">
@@ -1470,10 +1527,10 @@
         <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23">
@@ -1484,10 +1541,10 @@
         <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24">
@@ -1498,10 +1555,10 @@
         <v>7</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D24" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25">
@@ -1512,10 +1569,10 @@
         <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26">
@@ -1526,10 +1583,10 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D26" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27">
@@ -1540,10 +1597,10 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28">
@@ -1554,10 +1611,10 @@
         <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29">
@@ -1568,7 +1625,7 @@
         <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30">
@@ -1579,10 +1636,10 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D30" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31">
@@ -1593,10 +1650,10 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32">
@@ -1607,10 +1664,10 @@
         <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33">
@@ -1621,10 +1678,10 @@
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34">
@@ -1635,10 +1692,10 @@
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D34" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35">
@@ -1649,10 +1706,10 @@
         <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36">
@@ -1663,10 +1720,10 @@
         <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37">
@@ -1677,10 +1734,10 @@
         <v>4</v>
       </c>
       <c r="C37" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1714,60 +1771,60 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="B1" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="C1" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="D1" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="E1" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="F1" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="G1" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="H1" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="I1" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="J1" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="K1" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="L1" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1776,27 +1833,27 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1828,13 +1885,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="B4" t="n">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1866,19 +1923,19 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1887,30 +1944,30 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="B6" t="n">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1942,13 +1999,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="B7" t="n">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1980,13 +2037,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -2018,13 +2075,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -2056,13 +2113,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -2094,13 +2151,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="B11" t="n">
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -2132,22 +2189,22 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -2156,27 +2213,27 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -2208,13 +2265,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -2246,19 +2303,19 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2267,30 +2324,30 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -2322,13 +2379,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B17" t="n">
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -2360,13 +2417,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B18" t="n">
         <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -2398,13 +2455,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B19" t="n">
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -2436,13 +2493,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B20" t="n">
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -2485,54 +2542,54 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="B1" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="C1" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="D1" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="E1" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="F1" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="G1" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="H1" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="I1" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="J1" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -2541,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -2549,13 +2606,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -2581,13 +2638,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="B4" t="n">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -2613,19 +2670,19 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2634,24 +2691,24 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="B6" t="n">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -2677,13 +2734,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="B7" t="n">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -2709,22 +2766,22 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -2733,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -2741,13 +2798,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -2773,13 +2830,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -2805,19 +2862,19 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2826,24 +2883,24 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -2869,13 +2926,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="B13" t="n">
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -2901,13 +2958,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="B14" t="n">
         <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -2933,13 +2990,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="B15" t="n">
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -2965,13 +3022,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="B16" t="n">
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -2997,13 +3054,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3029,13 +3086,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="B18" t="n">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -3061,13 +3118,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="B19" t="n">
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -3093,13 +3150,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="B20" t="n">
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -3136,60 +3193,60 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="B1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="C1" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="D1" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="E1" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="F1" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="G1" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="H1" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="I1" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="J1" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="K1" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="L1" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="M1" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="n">
-        <v>46298</v>
+        <v>46302</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="C2" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="E2" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
@@ -3218,19 +3275,19 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>46298</v>
+        <v>46302</v>
       </c>
       <c r="B3" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="C3" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D3" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="E3" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>

--- a/padel_2026.xlsx
+++ b/padel_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lcalle\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C685BED4-19F3-4E50-B84D-6B5C55037736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FBBA1B-24AB-4B2A-A0A7-FD32FED56207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="resultados" sheetId="1" r:id="rId1"/>
@@ -1739,7 +1739,7 @@
         <v>115</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>117</v>
@@ -1777,7 +1777,7 @@
         <v>115</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>118</v>
@@ -1815,7 +1815,7 @@
         <v>115</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>119</v>
@@ -1853,7 +1853,7 @@
         <v>115</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
         <v>120</v>
@@ -1891,7 +1891,7 @@
         <v>115</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
         <v>121</v>
@@ -2119,7 +2119,7 @@
         <v>127</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="s">
         <v>129</v>
@@ -2157,7 +2157,7 @@
         <v>127</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="s">
         <v>130</v>
@@ -2195,7 +2195,7 @@
         <v>127</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C15" t="s">
         <v>131</v>
@@ -2233,7 +2233,7 @@
         <v>127</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="s">
         <v>132</v>
@@ -2498,7 +2498,7 @@
         <v>143</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>117</v>
@@ -2530,7 +2530,7 @@
         <v>143</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>118</v>
@@ -2562,7 +2562,7 @@
         <v>143</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>119</v>
@@ -2594,7 +2594,7 @@
         <v>143</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
         <v>120</v>
@@ -2626,7 +2626,7 @@
         <v>143</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
         <v>121</v>
@@ -2690,7 +2690,7 @@
         <v>144</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
         <v>129</v>
@@ -2722,7 +2722,7 @@
         <v>144</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
         <v>130</v>
@@ -2754,7 +2754,7 @@
         <v>144</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
         <v>131</v>
@@ -2786,7 +2786,7 @@
         <v>144</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C12" t="s">
         <v>132</v>

--- a/padel_2026.xlsx
+++ b/padel_2026.xlsx
@@ -3,22 +3,22 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="0" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="resultados" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="listas" sheetId="19" state="visible" r:id="rId2"/>
     <sheet name="participantes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="clasificacion_auto" sheetId="184" state="visible" r:id="rId4"/>
-    <sheet name="clasificacion" sheetId="185" state="visible" r:id="rId5"/>
-    <sheet name="historial_partidos" sheetId="186" state="visible" r:id="rId6"/>
+    <sheet name="clasificacion_auto" sheetId="190" state="visible" r:id="rId4"/>
+    <sheet name="clasificacion" sheetId="191" state="visible" r:id="rId5"/>
+    <sheet name="historial_partidos" sheetId="192" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="218">
   <si>
     <t>Mediocre alto</t>
   </si>
@@ -323,6 +323,21 @@
     <t>antonio.fernandez.alcalde@hacienda.gob.es</t>
   </si>
   <si>
+    <t>3ª vuelta</t>
+  </si>
+  <si>
+    <t>6-4, 6-1</t>
+  </si>
+  <si>
+    <t>4-6, 1-6</t>
+  </si>
+  <si>
+    <t>3-6, 0-6</t>
+  </si>
+  <si>
+    <t>6-3, 6-0</t>
+  </si>
+  <si>
     <t>GRUPO</t>
   </si>
   <si>
@@ -398,21 +413,21 @@
     <t>mediocre medio</t>
   </si>
   <si>
+    <t>Leticia-Alfonso</t>
+  </si>
+  <si>
+    <t>Alba-Bonilla</t>
+  </si>
+  <si>
+    <t>Miguel Ángel-Juanjo</t>
+  </si>
+  <si>
+    <t>Alberto-Esperanza</t>
+  </si>
+  <si>
     <t>Teresa-Álvaro</t>
   </si>
   <si>
-    <t>Alba-Bonilla</t>
-  </si>
-  <si>
-    <t>Alberto-Esperanza</t>
-  </si>
-  <si>
-    <t>Leticia-Alfonso</t>
-  </si>
-  <si>
-    <t>Miguel Ángel-Juanjo</t>
-  </si>
-  <si>
     <t>Tito-Yolanda</t>
   </si>
   <si>
@@ -467,19 +482,43 @@
     <t>PUNTOS_ACUM</t>
   </si>
   <si>
-    <t>3ª vuelta</t>
-  </si>
-  <si>
-    <t>6-4, 6-1</t>
-  </si>
-  <si>
-    <t>4-6, 1-6</t>
-  </si>
-  <si>
-    <t>3-6, 0-6</t>
-  </si>
-  <si>
-    <t>6-3, 6-0</t>
+    <t>1ª vuelta</t>
+  </si>
+  <si>
+    <t>Gana</t>
+  </si>
+  <si>
+    <t>Pierde</t>
+  </si>
+  <si>
+    <t>6-7, 2-6</t>
+  </si>
+  <si>
+    <t>7-6, 6-2</t>
+  </si>
+  <si>
+    <t>7-5, 3-3</t>
+  </si>
+  <si>
+    <t>5-7,3-3</t>
+  </si>
+  <si>
+    <t>6-3, 6-7, 10-3</t>
+  </si>
+  <si>
+    <t>6-3, 2-6, 15-13</t>
+  </si>
+  <si>
+    <t>3-6, 6-2, 13-15</t>
+  </si>
+  <si>
+    <t>1-6, 4-6, 10-10</t>
+  </si>
+  <si>
+    <t>6-1, 4-1, 10-10</t>
+  </si>
+  <si>
+    <t>3-6, 7-6, 3-10</t>
   </si>
   <si>
     <t xml:space="preserve">GRUPO</t>
@@ -521,67 +560,67 @@
     <t xml:space="preserve">mediocre alto</t>
   </si>
   <si>
+    <t xml:space="preserve">Temes-Sergio Payo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceci-Ángel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuño-Jorge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salva-Alberto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrés-J.J.Varas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fla-Delicattesen</t>
   </si>
   <si>
-    <t xml:space="preserve">Temes-Sergio Payo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrés-J.J.Varas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceci-Ángel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuño-Jorge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salva-Alberto</t>
-  </si>
-  <si>
     <t xml:space="preserve">mediocre bajo</t>
   </si>
   <si>
+    <t xml:space="preserve">Mario-Lourdes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cristina-Alberto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luis-Lina</t>
+  </si>
+  <si>
     <t xml:space="preserve">Carmen-Mónica</t>
   </si>
   <si>
-    <t xml:space="preserve">Cristina-Alberto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luis-Lina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mario-Lourdes</t>
-  </si>
-  <si>
     <t xml:space="preserve">mediocre medio</t>
   </si>
   <si>
+    <t xml:space="preserve">Miguel Ángel-Juanjo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alberto-Esperanza</t>
+  </si>
+  <si>
     <t xml:space="preserve">Leticia-Alfonso</t>
   </si>
   <si>
     <t xml:space="preserve">Alba-Bonilla</t>
   </si>
   <si>
-    <t xml:space="preserve">Miguel Ángel-Juanjo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alberto-Esperanza</t>
+    <t xml:space="preserve">Marta-Víctor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natalia-Jose Antonio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tito-Yolanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tania-Laura</t>
   </si>
   <si>
     <t xml:space="preserve">Teresa-Álvaro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tito-Yolanda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tania-Laura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natalia-Jose Antonio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marta-Víctor</t>
   </si>
   <si>
     <t xml:space="preserve">P. JUGADOS</t>
@@ -1041,10 +1080,10 @@
         <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>150</v>
+        <v>102</v>
       </c>
       <c r="F2" t="s">
-        <v>151</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3">
@@ -1061,14 +1100,111 @@
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>152</v>
+        <v>104</v>
       </c>
       <c r="F3" t="s">
-        <v>153</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4">
-      <c r="E4" s="1"/>
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>161</v>
+      </c>
+      <c r="F6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>164</v>
+      </c>
+      <c r="F8" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="10">
       <c r="V10" s="1"/>
@@ -1146,7 +1282,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>149</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
@@ -1786,60 +1922,60 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="B1" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="C1" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="D1" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="E1" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="F1" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="G1" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="H1" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="I1" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="J1" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="K1" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="L1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1848,36 +1984,36 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1886,33 +2022,33 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1921,36 +2057,36 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1959,30 +2095,30 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -2014,13 +2150,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="B7" t="n">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -2052,22 +2188,22 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -2076,33 +2212,33 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -2111,30 +2247,30 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -2166,13 +2302,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="B11" t="n">
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -2204,57 +2340,57 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="D12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" t="n">
         <v>3</v>
       </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B13" t="n">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D13" t="n">
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -2263,39 +2399,39 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L13" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -2304,33 +2440,33 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B15" t="n">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2339,36 +2475,36 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B16" t="n">
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2377,30 +2513,30 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B17" t="n">
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -2432,13 +2568,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B18" t="n">
         <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -2470,13 +2606,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B19" t="n">
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -2508,19 +2644,19 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B20" t="n">
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2529,19 +2665,19 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2557,54 +2693,54 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="B1" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="C1" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="D1" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="E1" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="F1" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="G1" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="H1" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="I1" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="J1" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -2613,30 +2749,30 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -2645,27 +2781,27 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2674,30 +2810,30 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2706,24 +2842,24 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -2749,13 +2885,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="B7" t="n">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -2781,13 +2917,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
@@ -2805,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -2813,22 +2949,22 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -2837,21 +2973,21 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -2877,13 +3013,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="B11" t="n">
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -2909,54 +3045,54 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -2965,7 +3101,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2973,22 +3109,22 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -2997,7 +3133,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -3005,19 +3141,19 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -3026,24 +3162,24 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -3069,13 +3205,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3101,13 +3237,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B18" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
         <v>196</v>
-      </c>
-      <c r="B18" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" t="s">
-        <v>175</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -3133,13 +3269,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -3165,13 +3301,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -3208,145 +3344,145 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="B1" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="C1" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="D1" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="E1" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="F1" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="G1" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="H1" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="I1" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="J1" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="K1" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="L1" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="M1" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46310</v>
+        <v>46317</v>
       </c>
       <c r="B2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C2" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D2" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E2" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46310</v>
+        <v>46317</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C3" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D3" t="s">
         <v>181</v>
       </c>
       <c r="E3" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46310</v>
+        <v>46317</v>
       </c>
       <c r="B4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C4" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E4" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
@@ -3372,31 +3508,31 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46310</v>
+        <v>46317</v>
       </c>
       <c r="B5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C5" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E5" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>3</v>
@@ -3408,7 +3544,417 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" t="s">
+        <v>215</v>
+      </c>
+      <c r="D6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C7" t="s">
+        <v>215</v>
+      </c>
+      <c r="D7" t="s">
+        <v>187</v>
+      </c>
+      <c r="E7" t="s">
+        <v>216</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C8" t="s">
+        <v>215</v>
+      </c>
+      <c r="D8" t="s">
+        <v>193</v>
+      </c>
+      <c r="E8" t="s">
+        <v>216</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E9" t="s">
+        <v>216</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B10" t="s">
+        <v>191</v>
+      </c>
+      <c r="C10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D10" t="s">
+        <v>192</v>
+      </c>
+      <c r="E10" t="s">
+        <v>217</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B11" t="s">
+        <v>191</v>
+      </c>
+      <c r="C11" t="s">
+        <v>215</v>
+      </c>
+      <c r="D11" t="s">
+        <v>192</v>
+      </c>
+      <c r="E11" t="s">
+        <v>216</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B12" t="s">
+        <v>191</v>
+      </c>
+      <c r="C12" t="s">
+        <v>215</v>
+      </c>
+      <c r="D12" t="s">
+        <v>192</v>
+      </c>
+      <c r="E12" t="s">
+        <v>216</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B13" t="s">
+        <v>191</v>
+      </c>
+      <c r="C13" t="s">
+        <v>215</v>
+      </c>
+      <c r="D13" t="s">
+        <v>199</v>
+      </c>
+      <c r="E13" t="s">
+        <v>217</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B14" t="s">
+        <v>191</v>
+      </c>
+      <c r="C14" t="s">
+        <v>215</v>
+      </c>
+      <c r="D14" t="s">
+        <v>200</v>
+      </c>
+      <c r="E14" t="s">
+        <v>217</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B15" t="s">
+        <v>191</v>
+      </c>
+      <c r="C15" t="s">
+        <v>215</v>
+      </c>
+      <c r="D15" t="s">
+        <v>200</v>
+      </c>
+      <c r="E15" t="s">
+        <v>217</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/padel_2026.xlsx
+++ b/padel_2026.xlsx
@@ -9,9 +9,9 @@
     <sheet name="resultados" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="listas" sheetId="19" state="visible" r:id="rId2"/>
     <sheet name="participantes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="clasificacion_auto" sheetId="190" state="visible" r:id="rId4"/>
-    <sheet name="clasificacion" sheetId="191" state="visible" r:id="rId5"/>
-    <sheet name="historial_partidos" sheetId="192" state="visible" r:id="rId6"/>
+    <sheet name="clasificacion_auto" sheetId="193" state="visible" r:id="rId4"/>
+    <sheet name="clasificacion" sheetId="194" state="visible" r:id="rId5"/>
+    <sheet name="historial_partidos" sheetId="195" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -2917,86 +2917,86 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -3013,19 +3013,19 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B11" t="n">
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -3034,13 +3034,13 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -3048,19 +3048,19 @@
         <v>208</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>2</v>
@@ -3080,19 +3080,19 @@
         <v>208</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -3101,7 +3101,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -3112,19 +3112,19 @@
         <v>208</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -3133,7 +3133,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -3144,16 +3144,16 @@
         <v>208</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -3162,13 +3162,13 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3176,16 +3176,16 @@
         <v>208</v>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -3194,33 +3194,33 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -3237,19 +3237,19 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -3258,24 +3258,24 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -3301,13 +3301,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>

--- a/padel_2026.xlsx
+++ b/padel_2026.xlsx
@@ -9,16 +9,16 @@
     <sheet name="resultados" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="listas" sheetId="19" state="visible" r:id="rId2"/>
     <sheet name="participantes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="clasificacion_auto" sheetId="193" state="visible" r:id="rId4"/>
-    <sheet name="clasificacion" sheetId="194" state="visible" r:id="rId5"/>
-    <sheet name="historial_partidos" sheetId="195" state="visible" r:id="rId6"/>
+    <sheet name="clasificacion_auto" sheetId="196" state="visible" r:id="rId4"/>
+    <sheet name="clasificacion" sheetId="197" state="visible" r:id="rId5"/>
+    <sheet name="historial_partidos" sheetId="198" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="221">
   <si>
     <t>Mediocre alto</t>
   </si>
@@ -338,6 +338,36 @@
     <t>6-3, 6-0</t>
   </si>
   <si>
+    <t>6-7, 2-6</t>
+  </si>
+  <si>
+    <t>7-6, 6-2</t>
+  </si>
+  <si>
+    <t>7-5, 3-3</t>
+  </si>
+  <si>
+    <t>5-7,3-3</t>
+  </si>
+  <si>
+    <t>6-3, 6-7, 10-3</t>
+  </si>
+  <si>
+    <t>6-3, 2-6, 15-13</t>
+  </si>
+  <si>
+    <t>3-6, 6-2, 13-15</t>
+  </si>
+  <si>
+    <t>1-6, 4-6, 10-10</t>
+  </si>
+  <si>
+    <t>6-1, 4-1, 10-10</t>
+  </si>
+  <si>
+    <t>3-6, 7-6, 3-10</t>
+  </si>
+  <si>
     <t>GRUPO</t>
   </si>
   <si>
@@ -377,69 +407,69 @@
     <t>mediocre alto</t>
   </si>
   <si>
+    <t>Temes-Sergio Payo</t>
+  </si>
+  <si>
+    <t>Ceci-Ángel</t>
+  </si>
+  <si>
+    <t>Nuño-Jorge</t>
+  </si>
+  <si>
+    <t>Salva-Alberto</t>
+  </si>
+  <si>
+    <t>Andrés-J.J.Varas</t>
+  </si>
+  <si>
     <t>Fla-Delicattesen</t>
   </si>
   <si>
-    <t>Temes-Sergio Payo</t>
-  </si>
-  <si>
-    <t>Andrés-J.J.Varas</t>
-  </si>
-  <si>
-    <t>Ceci-Ángel</t>
-  </si>
-  <si>
-    <t>Nuño-Jorge</t>
-  </si>
-  <si>
-    <t>Salva-Alberto</t>
-  </si>
-  <si>
     <t>mediocre bajo</t>
   </si>
   <si>
+    <t>Mario-Lourdes</t>
+  </si>
+  <si>
+    <t>Cristina-Alberto</t>
+  </si>
+  <si>
+    <t>Luis-Lina</t>
+  </si>
+  <si>
     <t>Carmen-Mónica</t>
   </si>
   <si>
-    <t>Cristina-Alberto</t>
-  </si>
-  <si>
-    <t>Luis-Lina</t>
-  </si>
-  <si>
-    <t>Mario-Lourdes</t>
-  </si>
-  <si>
     <t>mediocre medio</t>
   </si>
   <si>
+    <t>Miguel Ángel-Juanjo</t>
+  </si>
+  <si>
+    <t>Alberto-Esperanza</t>
+  </si>
+  <si>
     <t>Leticia-Alfonso</t>
   </si>
   <si>
     <t>Alba-Bonilla</t>
   </si>
   <si>
-    <t>Miguel Ángel-Juanjo</t>
-  </si>
-  <si>
-    <t>Alberto-Esperanza</t>
+    <t>Marta-Víctor</t>
+  </si>
+  <si>
+    <t>Natalia-Jose Antonio</t>
+  </si>
+  <si>
+    <t>Tito-Yolanda</t>
+  </si>
+  <si>
+    <t>Tania-Laura</t>
   </si>
   <si>
     <t>Teresa-Álvaro</t>
   </si>
   <si>
-    <t>Tito-Yolanda</t>
-  </si>
-  <si>
-    <t>Tania-Laura</t>
-  </si>
-  <si>
-    <t>Natalia-Jose Antonio</t>
-  </si>
-  <si>
-    <t>Marta-Víctor</t>
-  </si>
-  <si>
     <t>P. JUGADOS</t>
   </si>
   <si>
@@ -491,34 +521,10 @@
     <t>Pierde</t>
   </si>
   <si>
-    <t>6-7, 2-6</t>
-  </si>
-  <si>
-    <t>7-6, 6-2</t>
-  </si>
-  <si>
-    <t>7-5, 3-3</t>
-  </si>
-  <si>
-    <t>5-7,3-3</t>
-  </si>
-  <si>
-    <t>6-3, 6-7, 10-3</t>
-  </si>
-  <si>
-    <t>6-3, 2-6, 15-13</t>
-  </si>
-  <si>
-    <t>3-6, 6-2, 13-15</t>
-  </si>
-  <si>
-    <t>1-6, 4-6, 10-10</t>
-  </si>
-  <si>
-    <t>6-1, 4-1, 10-10</t>
-  </si>
-  <si>
-    <t>3-6, 7-6, 3-10</t>
+    <t>7-6, 4-6</t>
+  </si>
+  <si>
+    <t>6-7,6-4</t>
   </si>
   <si>
     <t xml:space="preserve">GRUPO</t>
@@ -560,10 +566,16 @@
     <t xml:space="preserve">mediocre alto</t>
   </si>
   <si>
+    <t xml:space="preserve">Ceci-Ángel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Temes-Sergio Payo</t>
   </si>
   <si>
-    <t xml:space="preserve">Ceci-Ángel</t>
+    <t xml:space="preserve">Andrés-J.J.Varas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fla-Delicattesen</t>
   </si>
   <si>
     <t xml:space="preserve">Nuño-Jorge</t>
@@ -572,27 +584,21 @@
     <t xml:space="preserve">Salva-Alberto</t>
   </si>
   <si>
-    <t xml:space="preserve">Andrés-J.J.Varas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fla-Delicattesen</t>
-  </si>
-  <si>
     <t xml:space="preserve">mediocre bajo</t>
   </si>
   <si>
     <t xml:space="preserve">Mario-Lourdes</t>
   </si>
   <si>
+    <t xml:space="preserve">Carmen-Mónica</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cristina-Alberto</t>
   </si>
   <si>
     <t xml:space="preserve">Luis-Lina</t>
   </si>
   <si>
-    <t xml:space="preserve">Carmen-Mónica</t>
-  </si>
-  <si>
     <t xml:space="preserve">mediocre medio</t>
   </si>
   <si>
@@ -605,24 +611,24 @@
     <t xml:space="preserve">Leticia-Alfonso</t>
   </si>
   <si>
+    <t xml:space="preserve">Marta-Víctor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tito-Yolanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teresa-Álvaro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tania-Laura</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alba-Bonilla</t>
   </si>
   <si>
-    <t xml:space="preserve">Marta-Víctor</t>
-  </si>
-  <si>
     <t xml:space="preserve">Natalia-Jose Antonio</t>
   </si>
   <si>
-    <t xml:space="preserve">Tito-Yolanda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tania-Laura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teresa-Álvaro</t>
-  </si>
-  <si>
     <t xml:space="preserve">P. JUGADOS</t>
   </si>
   <si>
@@ -668,10 +674,13 @@
     <t xml:space="preserve">1ª vuelta</t>
   </si>
   <si>
+    <t xml:space="preserve">Pierde</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gana</t>
   </si>
   <si>
-    <t xml:space="preserve">Pierde</t>
+    <t xml:space="preserve">Empata</t>
   </si>
 </sst>
 </file>
@@ -679,7 +688,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -691,12 +700,19 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <u val="single"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -724,13 +740,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1120,10 +1137,10 @@
         <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>157</v>
+        <v>106</v>
       </c>
       <c r="F4" t="s">
-        <v>158</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5">
@@ -1140,10 +1157,10 @@
         <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>159</v>
+        <v>108</v>
       </c>
       <c r="F5" t="s">
-        <v>160</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6">
@@ -1160,10 +1177,10 @@
         <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="F6" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7">
@@ -1180,10 +1197,10 @@
         <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="F7" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8">
@@ -1200,10 +1217,30 @@
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>164</v>
+        <v>113</v>
       </c>
       <c r="F8" t="s">
-        <v>165</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" t="s">
+        <v>167</v>
+      </c>
+      <c r="F9" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="10">
@@ -1922,51 +1959,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
@@ -1998,13 +2035,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -2036,7 +2073,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
@@ -2074,7 +2111,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
@@ -2112,13 +2149,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -2150,13 +2187,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B7" t="n">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -2188,13 +2225,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
@@ -2226,7 +2263,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
@@ -2264,13 +2301,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -2302,13 +2339,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B11" t="n">
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -2340,13 +2377,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D12" t="n">
         <v>6</v>
@@ -2378,13 +2415,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B13" t="n">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D13" t="n">
         <v>3</v>
@@ -2416,13 +2453,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -2454,54 +2491,54 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B15" t="n">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L15" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B16" t="n">
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -2510,39 +2547,39 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B17" t="n">
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -2551,36 +2588,36 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B18" t="n">
         <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -2589,30 +2626,30 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B19" t="n">
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -2644,13 +2681,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B20" t="n">
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -2693,45 +2730,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="J1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
@@ -2757,13 +2794,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -2789,7 +2826,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
@@ -2821,7 +2858,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
@@ -2853,13 +2890,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -2885,13 +2922,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B7" t="n">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -2917,13 +2954,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
@@ -2949,13 +2986,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -2981,13 +3018,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
@@ -3013,48 +3050,48 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B11" t="n">
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B12" t="n">
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -3063,33 +3100,33 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B13" t="n">
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -3098,30 +3135,30 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B14" t="n">
         <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -3130,24 +3167,24 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B15" t="n">
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -3173,13 +3210,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B16" t="n">
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -3205,13 +3242,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D17" t="n">
         <v>3</v>
@@ -3237,7 +3274,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B18" t="n">
         <v>2</v>
@@ -3269,13 +3306,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B19" t="n">
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -3301,13 +3338,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B20" t="n">
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -3344,101 +3381,101 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G1" t="s">
+        <v>178</v>
+      </c>
+      <c r="H1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J1" t="s">
+        <v>216</v>
+      </c>
+      <c r="K1" t="s">
+        <v>174</v>
+      </c>
+      <c r="L1" t="s">
         <v>175</v>
       </c>
-      <c r="G1" t="s">
+      <c r="M1" t="s">
         <v>176</v>
       </c>
-      <c r="H1" t="s">
-        <v>170</v>
-      </c>
-      <c r="I1" t="s">
-        <v>213</v>
-      </c>
-      <c r="J1" t="s">
-        <v>214</v>
-      </c>
-      <c r="K1" t="s">
-        <v>172</v>
-      </c>
-      <c r="L1" t="s">
-        <v>173</v>
-      </c>
-      <c r="M1" t="s">
-        <v>174</v>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="4" t="n">
         <v>46317</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D2" t="s">
         <v>184</v>
       </c>
       <c r="E2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" t="s">
         <v>217</v>
       </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C3" t="s">
-        <v>215</v>
-      </c>
       <c r="D3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -3466,61 +3503,61 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="4" t="n">
         <v>46317</v>
       </c>
       <c r="B4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D4" t="s">
         <v>185</v>
       </c>
       <c r="E4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" t="s">
         <v>217</v>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B5" t="s">
-        <v>179</v>
-      </c>
-      <c r="C5" t="s">
-        <v>215</v>
-      </c>
       <c r="D5" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E5" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -3548,61 +3585,61 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="4" t="n">
         <v>46317</v>
       </c>
       <c r="B6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D6" t="s">
         <v>190</v>
       </c>
       <c r="E6" t="s">
+        <v>218</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C7" t="s">
         <v>217</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C7" t="s">
-        <v>215</v>
-      </c>
       <c r="D7" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E7" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -3630,20 +3667,20 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="4" t="n">
         <v>46317</v>
       </c>
       <c r="B8" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E8" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -3671,20 +3708,20 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="4" t="n">
         <v>46317</v>
       </c>
       <c r="B9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D9" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E9" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -3712,102 +3749,102 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="4" t="n">
         <v>46317</v>
       </c>
       <c r="B10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D10" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E10" t="s">
+        <v>220</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B11" t="s">
+        <v>193</v>
+      </c>
+      <c r="C11" t="s">
         <v>217</v>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="D11" t="s">
+        <v>194</v>
+      </c>
+      <c r="E11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
         <v>46317</v>
       </c>
-      <c r="B11" t="s">
-        <v>191</v>
-      </c>
-      <c r="C11" t="s">
-        <v>215</v>
-      </c>
-      <c r="D11" t="s">
-        <v>192</v>
-      </c>
-      <c r="E11" t="s">
-        <v>216</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>46317</v>
-      </c>
       <c r="B12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C12" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E12" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
@@ -3819,142 +3856,224 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
         <v>3</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B13" t="s">
+        <v>193</v>
+      </c>
+      <c r="C13" t="s">
+        <v>217</v>
+      </c>
+      <c r="D13" t="s">
+        <v>194</v>
+      </c>
+      <c r="E13" t="s">
+        <v>219</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="n">
         <v>6</v>
       </c>
-      <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
         <v>46317</v>
       </c>
-      <c r="B13" t="s">
-        <v>191</v>
-      </c>
-      <c r="C13" t="s">
-        <v>215</v>
-      </c>
-      <c r="D13" t="s">
-        <v>199</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="B14" t="s">
+        <v>193</v>
+      </c>
+      <c r="C14" t="s">
         <v>217</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B14" t="s">
-        <v>191</v>
-      </c>
-      <c r="C14" t="s">
-        <v>215</v>
       </c>
       <c r="D14" t="s">
         <v>200</v>
       </c>
       <c r="E14" t="s">
+        <v>218</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B15" t="s">
+        <v>193</v>
+      </c>
+      <c r="C15" t="s">
         <v>217</v>
       </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="D15" t="s">
+        <v>199</v>
+      </c>
+      <c r="E15" t="s">
+        <v>218</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
         <v>46317</v>
       </c>
-      <c r="B15" t="s">
-        <v>191</v>
-      </c>
-      <c r="C15" t="s">
-        <v>215</v>
-      </c>
-      <c r="D15" t="s">
-        <v>200</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="B16" t="s">
+        <v>193</v>
+      </c>
+      <c r="C16" t="s">
         <v>217</v>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2</v>
+      <c r="D16" t="s">
+        <v>199</v>
+      </c>
+      <c r="E16" t="s">
+        <v>218</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B17" t="s">
+        <v>193</v>
+      </c>
+      <c r="C17" t="s">
+        <v>217</v>
+      </c>
+      <c r="D17" t="s">
+        <v>198</v>
+      </c>
+      <c r="E17" t="s">
+        <v>220</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/padel_2026.xlsx
+++ b/padel_2026.xlsx
@@ -9,16 +9,16 @@
     <sheet name="resultados" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="listas" sheetId="19" state="visible" r:id="rId2"/>
     <sheet name="participantes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="clasificacion_auto" sheetId="196" state="visible" r:id="rId4"/>
-    <sheet name="clasificacion" sheetId="197" state="visible" r:id="rId5"/>
-    <sheet name="historial_partidos" sheetId="198" state="visible" r:id="rId6"/>
+    <sheet name="clasificacion_auto" sheetId="199" state="visible" r:id="rId4"/>
+    <sheet name="clasificacion" sheetId="200" state="visible" r:id="rId5"/>
+    <sheet name="historial_partidos" sheetId="201" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="222">
   <si>
     <t>Mediocre alto</t>
   </si>
@@ -359,15 +359,15 @@
     <t>3-6, 6-2, 13-15</t>
   </si>
   <si>
-    <t>1-6, 4-6, 10-10</t>
-  </si>
-  <si>
-    <t>6-1, 4-1, 10-10</t>
-  </si>
-  <si>
     <t>3-6, 7-6, 3-10</t>
   </si>
   <si>
+    <t>7-6, 4-6</t>
+  </si>
+  <si>
+    <t>6-7,6-4</t>
+  </si>
+  <si>
     <t>GRUPO</t>
   </si>
   <si>
@@ -407,10 +407,16 @@
     <t>mediocre alto</t>
   </si>
   <si>
+    <t>Ceci-Ángel</t>
+  </si>
+  <si>
     <t>Temes-Sergio Payo</t>
   </si>
   <si>
-    <t>Ceci-Ángel</t>
+    <t>Andrés-J.J.Varas</t>
+  </si>
+  <si>
+    <t>Fla-Delicattesen</t>
   </si>
   <si>
     <t>Nuño-Jorge</t>
@@ -419,27 +425,21 @@
     <t>Salva-Alberto</t>
   </si>
   <si>
-    <t>Andrés-J.J.Varas</t>
-  </si>
-  <si>
-    <t>Fla-Delicattesen</t>
-  </si>
-  <si>
     <t>mediocre bajo</t>
   </si>
   <si>
     <t>Mario-Lourdes</t>
   </si>
   <si>
+    <t>Carmen-Mónica</t>
+  </si>
+  <si>
     <t>Cristina-Alberto</t>
   </si>
   <si>
     <t>Luis-Lina</t>
   </si>
   <si>
-    <t>Carmen-Mónica</t>
-  </si>
-  <si>
     <t>mediocre medio</t>
   </si>
   <si>
@@ -452,24 +452,24 @@
     <t>Leticia-Alfonso</t>
   </si>
   <si>
+    <t>Marta-Víctor</t>
+  </si>
+  <si>
+    <t>Tito-Yolanda</t>
+  </si>
+  <si>
+    <t>Teresa-Álvaro</t>
+  </si>
+  <si>
+    <t>Tania-Laura</t>
+  </si>
+  <si>
     <t>Alba-Bonilla</t>
   </si>
   <si>
-    <t>Marta-Víctor</t>
-  </si>
-  <si>
     <t>Natalia-Jose Antonio</t>
   </si>
   <si>
-    <t>Tito-Yolanda</t>
-  </si>
-  <si>
-    <t>Tania-Laura</t>
-  </si>
-  <si>
-    <t>Teresa-Álvaro</t>
-  </si>
-  <si>
     <t>P. JUGADOS</t>
   </si>
   <si>
@@ -515,16 +515,19 @@
     <t>1ª vuelta</t>
   </si>
   <si>
+    <t>Pierde</t>
+  </si>
+  <si>
     <t>Gana</t>
   </si>
   <si>
-    <t>Pierde</t>
-  </si>
-  <si>
-    <t>7-6, 4-6</t>
-  </si>
-  <si>
-    <t>6-7,6-4</t>
+    <t>Empata</t>
+  </si>
+  <si>
+    <t>1-6, 6-4, 10-10</t>
+  </si>
+  <si>
+    <t>6-1, 4-6, 10-10</t>
   </si>
   <si>
     <t xml:space="preserve">GRUPO</t>
@@ -605,19 +608,19 @@
     <t xml:space="preserve">Miguel Ángel-Juanjo</t>
   </si>
   <si>
+    <t xml:space="preserve">Leticia-Alfonso</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alberto-Esperanza</t>
   </si>
   <si>
-    <t xml:space="preserve">Leticia-Alfonso</t>
+    <t xml:space="preserve">Teresa-Álvaro</t>
   </si>
   <si>
     <t xml:space="preserve">Marta-Víctor</t>
   </si>
   <si>
     <t xml:space="preserve">Tito-Yolanda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teresa-Álvaro</t>
   </si>
   <si>
     <t xml:space="preserve">Tania-Laura</t>
@@ -1180,7 +1183,7 @@
         <v>110</v>
       </c>
       <c r="F6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7">
@@ -1217,10 +1220,10 @@
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="F8" t="s">
-        <v>114</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9">
@@ -1237,10 +1240,10 @@
         <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>167</v>
+        <v>114</v>
       </c>
       <c r="F9" t="s">
-        <v>168</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10">
@@ -1959,51 +1962,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
@@ -2035,13 +2038,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -2073,13 +2076,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -2111,13 +2114,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -2149,13 +2152,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -2187,13 +2190,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B7" t="n">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -2225,13 +2228,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
@@ -2263,13 +2266,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -2301,13 +2304,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -2339,13 +2342,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B11" t="n">
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -2377,13 +2380,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D12" t="n">
         <v>6</v>
@@ -2415,13 +2418,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B13" t="n">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D13" t="n">
         <v>3</v>
@@ -2445,65 +2448,65 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L13" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="L14" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B15" t="n">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2512,30 +2515,30 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="L15" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B16" t="n">
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
@@ -2559,59 +2562,59 @@
         <v>1</v>
       </c>
       <c r="K16" t="n">
+        <v>12</v>
+      </c>
+      <c r="L16" t="n">
         <v>11</v>
-      </c>
-      <c r="L16" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B17" t="n">
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L17" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B18" t="n">
         <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -2643,13 +2646,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B19" t="n">
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -2681,13 +2684,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B20" t="n">
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -2730,45 +2733,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
@@ -2794,13 +2797,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -2826,13 +2829,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -2858,13 +2861,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -2890,13 +2893,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -2922,13 +2925,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B7" t="n">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -2954,13 +2957,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
@@ -2986,13 +2989,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -3018,51 +3021,51 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B11" t="n">
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -3071,24 +3074,24 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B12" t="n">
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -3114,45 +3117,45 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B13" t="n">
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B14" t="n">
         <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -3178,13 +3181,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B15" t="n">
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -3210,13 +3213,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B16" t="n">
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -3242,13 +3245,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D17" t="n">
         <v>3</v>
@@ -3274,13 +3277,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B18" t="n">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -3306,13 +3309,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B19" t="n">
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -3338,13 +3341,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B20" t="n">
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -3381,43 +3384,43 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G1" t="s">
+        <v>179</v>
+      </c>
+      <c r="H1" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1" t="s">
+        <v>216</v>
+      </c>
+      <c r="J1" t="s">
+        <v>217</v>
+      </c>
+      <c r="K1" t="s">
+        <v>175</v>
+      </c>
+      <c r="L1" t="s">
+        <v>176</v>
+      </c>
+      <c r="M1" t="s">
         <v>177</v>
-      </c>
-      <c r="G1" t="s">
-        <v>178</v>
-      </c>
-      <c r="H1" t="s">
-        <v>172</v>
-      </c>
-      <c r="I1" t="s">
-        <v>215</v>
-      </c>
-      <c r="J1" t="s">
-        <v>216</v>
-      </c>
-      <c r="K1" t="s">
-        <v>174</v>
-      </c>
-      <c r="L1" t="s">
-        <v>175</v>
-      </c>
-      <c r="M1" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="2">
@@ -3425,16 +3428,16 @@
         <v>46317</v>
       </c>
       <c r="B2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -3466,16 +3469,16 @@
         <v>46317</v>
       </c>
       <c r="B3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -3507,16 +3510,16 @@
         <v>46317</v>
       </c>
       <c r="B4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -3548,16 +3551,16 @@
         <v>46317</v>
       </c>
       <c r="B5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -3589,16 +3592,16 @@
         <v>46317</v>
       </c>
       <c r="B6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -3630,16 +3633,16 @@
         <v>46317</v>
       </c>
       <c r="B7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -3671,37 +3674,37 @@
         <v>46317</v>
       </c>
       <c r="B8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -3712,16 +3715,16 @@
         <v>46317</v>
       </c>
       <c r="B9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D9" t="s">
         <v>196</v>
       </c>
       <c r="E9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -3753,16 +3756,16 @@
         <v>46317</v>
       </c>
       <c r="B10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D10" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -3794,16 +3797,16 @@
         <v>46317</v>
       </c>
       <c r="B11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -3835,16 +3838,16 @@
         <v>46317</v>
       </c>
       <c r="B12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
@@ -3876,16 +3879,16 @@
         <v>46317</v>
       </c>
       <c r="B13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F13" t="n">
         <v>2</v>
@@ -3917,16 +3920,16 @@
         <v>46317</v>
       </c>
       <c r="B14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -3958,16 +3961,16 @@
         <v>46317</v>
       </c>
       <c r="B15" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D15" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -3999,40 +4002,40 @@
         <v>46317</v>
       </c>
       <c r="B16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E16" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -4040,16 +4043,16 @@
         <v>46317</v>
       </c>
       <c r="B17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C17" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D17" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>

--- a/padel_2026.xlsx
+++ b/padel_2026.xlsx
@@ -9,9 +9,9 @@
     <sheet name="resultados" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="listas" sheetId="19" state="visible" r:id="rId2"/>
     <sheet name="participantes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="clasificacion_auto" sheetId="199" state="visible" r:id="rId4"/>
-    <sheet name="clasificacion" sheetId="200" state="visible" r:id="rId5"/>
-    <sheet name="historial_partidos" sheetId="201" state="visible" r:id="rId6"/>
+    <sheet name="clasificacion_auto" sheetId="202" state="visible" r:id="rId4"/>
+    <sheet name="clasificacion" sheetId="203" state="visible" r:id="rId5"/>
+    <sheet name="historial_partidos" sheetId="204" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -368,6 +368,12 @@
     <t>6-7,6-4</t>
   </si>
   <si>
+    <t>1-6, 6-4, 10-10</t>
+  </si>
+  <si>
+    <t>6-1, 4-6, 10-10</t>
+  </si>
+  <si>
     <t>GRUPO</t>
   </si>
   <si>
@@ -446,10 +452,13 @@
     <t>Miguel Ángel-Juanjo</t>
   </si>
   <si>
+    <t>Leticia-Alfonso</t>
+  </si>
+  <si>
     <t>Alberto-Esperanza</t>
   </si>
   <si>
-    <t>Leticia-Alfonso</t>
+    <t>Teresa-Álvaro</t>
   </si>
   <si>
     <t>Marta-Víctor</t>
@@ -458,9 +467,6 @@
     <t>Tito-Yolanda</t>
   </si>
   <si>
-    <t>Teresa-Álvaro</t>
-  </si>
-  <si>
     <t>Tania-Laura</t>
   </si>
   <si>
@@ -524,12 +530,6 @@
     <t>Empata</t>
   </si>
   <si>
-    <t>1-6, 6-4, 10-10</t>
-  </si>
-  <si>
-    <t>6-1, 4-6, 10-10</t>
-  </si>
-  <si>
     <t xml:space="preserve">GRUPO</t>
   </si>
   <si>
@@ -608,6 +608,9 @@
     <t xml:space="preserve">Miguel Ángel-Juanjo</t>
   </si>
   <si>
+    <t xml:space="preserve">Tito-Yolanda</t>
+  </si>
+  <si>
     <t xml:space="preserve">Leticia-Alfonso</t>
   </si>
   <si>
@@ -618,9 +621,6 @@
   </si>
   <si>
     <t xml:space="preserve">Marta-Víctor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tito-Yolanda</t>
   </si>
   <si>
     <t xml:space="preserve">Tania-Laura</t>
@@ -1220,10 +1220,10 @@
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>168</v>
+        <v>116</v>
       </c>
       <c r="F8" t="s">
-        <v>169</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9">
@@ -1247,6 +1247,24 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F10" t="s">
+        <v>103</v>
+      </c>
       <c r="V10" s="1"/>
     </row>
   </sheetData>
@@ -2392,7 +2410,7 @@
         <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
@@ -2401,19 +2419,19 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L12" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -2427,31 +2445,31 @@
         <v>196</v>
       </c>
       <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>3</v>
       </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2</v>
-      </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
@@ -2465,31 +2483,31 @@
         <v>197</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L14" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -2506,7 +2524,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2515,19 +2533,19 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>20</v>
       </c>
       <c r="L15" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -2544,7 +2562,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2553,19 +2571,19 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="L16" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -2600,10 +2618,10 @@
         <v>1</v>
       </c>
       <c r="K17" t="n">
+        <v>12</v>
+      </c>
+      <c r="L17" t="n">
         <v>11</v>
-      </c>
-      <c r="L17" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2969,7 +2987,7 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -2978,13 +2996,13 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -2998,25 +3016,25 @@
         <v>196</v>
       </c>
       <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>3</v>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2</v>
-      </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3030,25 +3048,25 @@
         <v>197</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3065,7 +3083,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -3074,13 +3092,13 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -3097,7 +3115,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -3106,13 +3124,13 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3443,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="B2" t="s">
         <v>182</v>
@@ -3466,7 +3484,7 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="B3" t="s">
         <v>182</v>
@@ -3507,7 +3525,7 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="B4" t="s">
         <v>182</v>
@@ -3548,7 +3566,7 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="B5" t="s">
         <v>182</v>
@@ -3589,7 +3607,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="B6" t="s">
         <v>189</v>
@@ -3630,7 +3648,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="B7" t="s">
         <v>189</v>
@@ -3671,7 +3689,7 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="B8" t="s">
         <v>194</v>
@@ -3680,7 +3698,7 @@
         <v>218</v>
       </c>
       <c r="D8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E8" t="s">
         <v>221</v>
@@ -3712,7 +3730,7 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="B9" t="s">
         <v>194</v>
@@ -3721,7 +3739,7 @@
         <v>218</v>
       </c>
       <c r="D9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E9" t="s">
         <v>220</v>
@@ -3753,7 +3771,7 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="B10" t="s">
         <v>194</v>
@@ -3762,7 +3780,7 @@
         <v>218</v>
       </c>
       <c r="D10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E10" t="s">
         <v>221</v>
@@ -3794,7 +3812,7 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="B11" t="s">
         <v>194</v>
@@ -3835,7 +3853,7 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="B12" t="s">
         <v>194</v>
@@ -3876,7 +3894,7 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="B13" t="s">
         <v>194</v>
@@ -3917,7 +3935,7 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="B14" t="s">
         <v>194</v>
@@ -3926,7 +3944,7 @@
         <v>218</v>
       </c>
       <c r="D14" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="E14" t="s">
         <v>219</v>
@@ -3941,24 +3959,24 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="B15" t="s">
         <v>194</v>
@@ -3967,7 +3985,7 @@
         <v>218</v>
       </c>
       <c r="D15" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E15" t="s">
         <v>219</v>
@@ -3999,7 +4017,7 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="B16" t="s">
         <v>194</v>
@@ -4008,31 +4026,31 @@
         <v>218</v>
       </c>
       <c r="D16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E16" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>1</v>
@@ -4040,7 +4058,7 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="B17" t="s">
         <v>194</v>
@@ -4049,7 +4067,7 @@
         <v>218</v>
       </c>
       <c r="D17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E17" t="s">
         <v>221</v>
@@ -4064,7 +4082,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -4076,6 +4094,88 @@
         <v>1</v>
       </c>
       <c r="M17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B18" t="s">
+        <v>194</v>
+      </c>
+      <c r="C18" t="s">
+        <v>218</v>
+      </c>
+      <c r="D18" t="s">
+        <v>196</v>
+      </c>
+      <c r="E18" t="s">
+        <v>221</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B19" t="s">
+        <v>194</v>
+      </c>
+      <c r="C19" t="s">
+        <v>218</v>
+      </c>
+      <c r="D19" t="s">
+        <v>196</v>
+      </c>
+      <c r="E19" t="s">
+        <v>220</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
